--- a/HAIR_FFU_CHECKLIST.xlsx
+++ b/HAIR_FFU_CHECKLIST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pgone-my.sharepoint.com/personal/yoon_j_3_pg_com/Documents/Desktop/project-tracker/project-tracker/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pgone.sharepoint.com/sites/POpriority/Shared Documents/Project Eagles/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{E10D6F3C-833B-4FC8-B55E-879DB113DA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{505539CC-531F-4BB4-9926-0E36B2ED2E16}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{E10D6F3C-833B-4FC8-B55E-879DB113DA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2D6E19D-4A74-4A39-928B-CAE1D333AE85}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{7BDEC216-E803-42B4-BF8A-9FDE670B68F3}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{7BDEC216-E803-42B4-BF8A-9FDE670B68F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$178</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="12"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2566,7 +2566,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>33</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>33</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>33</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>33</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>33</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>33</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>33</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>33</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>33</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>33</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>37</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>37</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>37</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>37</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>37</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>37</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>37</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>37</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>37</v>
       </c>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I118" s="6"/>
     </row>
-    <row r="119" spans="1:9" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>37</v>
       </c>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I119" s="7"/>
     </row>
-    <row r="120" spans="1:9" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>37</v>
       </c>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="I120" s="8"/>
     </row>
-    <row r="121" spans="1:9" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>38</v>
       </c>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="I121" s="8"/>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>38</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>38</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>38</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>38</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>38</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>38</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>38</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>38</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>38</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>38</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>38</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>38</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>38</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>38</v>
       </c>
@@ -3465,15 +3465,31 @@
   <autoFilter ref="A1:I178" xr:uid="{277571F3-9504-4C86-8E2D-BA4CDF05B089}">
     <filterColumn colId="0">
       <filters>
-        <filter val="EMART"/>
+        <filter val="COSTCO"/>
+        <filter val="TRADERS"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Calibri"&amp;10&amp;K000000 Business Use&amp;1#_x000D_</oddHeader>
+  </headerFooter>
+  <customProperties>
+    <customPr name="_pios_id" r:id="rId1"/>
+  </customProperties>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6c0e7a184c0233f586ea7baba2e967b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6204f9fca8cd82ddbd42930875406446" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
@@ -3696,15 +3712,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3717,13 +3724,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CB27180-59BD-4819-98AD-8351D161500A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{858AC7D4-6D6D-43B3-89B1-2B344252ACCC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{858AC7D4-6D6D-43B3-89B1-2B344252ACCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CB27180-59BD-4819-98AD-8351D161500A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="57147975-5687-4135-8263-39f5df548c17"/>
+    <ds:schemaRef ds:uri="96d24a6b-8465-4498-bb54-acea15c87a74"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C76A210F-437A-4119-9DFA-CFDD2A427257}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C76A210F-437A-4119-9DFA-CFDD2A427257}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="57147975-5687-4135-8263-39f5df548c17"/>
+    <ds:schemaRef ds:uri="96d24a6b-8465-4498-bb54-acea15c87a74"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/HAIR_FFU_CHECKLIST.xlsx
+++ b/HAIR_FFU_CHECKLIST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pgone.sharepoint.com/sites/POpriority/Shared Documents/Project Eagles/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{E10D6F3C-833B-4FC8-B55E-879DB113DA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2D6E19D-4A74-4A39-928B-CAE1D333AE85}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{E10D6F3C-833B-4FC8-B55E-879DB113DA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6851CAF-6EEA-44B9-A366-D5CC6D4B8775}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{7BDEC216-E803-42B4-BF8A-9FDE670B68F3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{7BDEC216-E803-42B4-BF8A-9FDE670B68F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$178</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentManualCount="12"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1490,7 +1490,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{277571F3-9504-4C86-8E2D-BA4CDF05B089}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1510,7 +1509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1521,7 +1520,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1532,7 +1531,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1543,7 +1542,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1554,7 +1553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1565,7 +1564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1576,7 +1575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1587,7 +1586,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1598,7 +1597,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1609,7 +1608,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1620,7 +1619,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1631,7 +1630,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1642,7 +1641,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1653,7 +1652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1664,7 +1663,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1675,7 +1674,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1686,7 +1685,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1697,7 +1696,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1708,7 +1707,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -1719,7 +1718,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1730,7 +1729,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -1741,7 +1740,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1752,7 +1751,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -1763,7 +1762,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -1774,7 +1773,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -1785,7 +1784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1796,7 +1795,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -1807,7 +1806,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -1818,7 +1817,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -1829,7 +1828,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1840,7 +1839,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -1851,7 +1850,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -1862,7 +1861,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -1873,7 +1872,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -1884,7 +1883,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -1895,7 +1894,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -1906,7 +1905,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -1917,7 +1916,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1928,7 +1927,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1939,7 +1938,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1950,7 +1949,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1961,7 +1960,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -1972,7 +1971,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1983,7 +1982,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -1994,7 +1993,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -2005,7 +2004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -2016,7 +2015,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>27</v>
       </c>
@@ -2038,7 +2037,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>27</v>
       </c>
@@ -2049,7 +2048,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>27</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>27</v>
       </c>
@@ -2071,7 +2070,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -2082,7 +2081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -2093,7 +2092,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>27</v>
       </c>
@@ -2104,7 +2103,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>27</v>
       </c>
@@ -2115,7 +2114,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>27</v>
       </c>
@@ -2126,7 +2125,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>27</v>
       </c>
@@ -2137,7 +2136,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>27</v>
       </c>
@@ -2148,7 +2147,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -2159,7 +2158,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -2170,7 +2169,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>27</v>
       </c>
@@ -2181,7 +2180,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>27</v>
       </c>
@@ -2192,7 +2191,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>27</v>
       </c>
@@ -2203,7 +2202,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>27</v>
       </c>
@@ -2214,7 +2213,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>27</v>
       </c>
@@ -2225,7 +2224,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>27</v>
       </c>
@@ -2236,7 +2235,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>27</v>
       </c>
@@ -2247,7 +2246,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>27</v>
       </c>
@@ -2258,7 +2257,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>27</v>
       </c>
@@ -2269,7 +2268,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>27</v>
       </c>
@@ -2280,7 +2279,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>27</v>
       </c>
@@ -2291,7 +2290,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>27</v>
       </c>
@@ -2302,7 +2301,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>27</v>
       </c>
@@ -2313,7 +2312,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>27</v>
       </c>
@@ -2324,7 +2323,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>27</v>
       </c>
@@ -2335,7 +2334,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>27</v>
       </c>
@@ -2346,7 +2345,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>27</v>
       </c>
@@ -2357,7 +2356,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>30</v>
       </c>
@@ -2368,7 +2367,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>30</v>
       </c>
@@ -2379,7 +2378,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>30</v>
       </c>
@@ -2390,7 +2389,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -2401,7 +2400,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>30</v>
       </c>
@@ -2412,7 +2411,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -2423,7 +2422,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>30</v>
       </c>
@@ -2434,7 +2433,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>30</v>
       </c>
@@ -2445,7 +2444,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>30</v>
       </c>
@@ -2456,7 +2455,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>30</v>
       </c>
@@ -2467,7 +2466,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>30</v>
       </c>
@@ -2478,7 +2477,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>30</v>
       </c>
@@ -2489,7 +2488,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>30</v>
       </c>
@@ -2500,7 +2499,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>30</v>
       </c>
@@ -2511,7 +2510,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>30</v>
       </c>
@@ -2522,7 +2521,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>30</v>
       </c>
@@ -2533,7 +2532,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>30</v>
       </c>
@@ -2544,7 +2543,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>30</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>30</v>
       </c>
@@ -2566,7 +2565,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>33</v>
       </c>
@@ -2577,7 +2576,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>33</v>
       </c>
@@ -2588,7 +2587,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>33</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>33</v>
       </c>
@@ -2610,7 +2609,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>33</v>
       </c>
@@ -2621,7 +2620,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>33</v>
       </c>
@@ -2632,7 +2631,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>33</v>
       </c>
@@ -2643,7 +2642,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>33</v>
       </c>
@@ -2654,7 +2653,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -2665,7 +2664,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -2676,7 +2675,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>33</v>
       </c>
@@ -2687,7 +2686,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>33</v>
       </c>
@@ -2988,7 +2987,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>45</v>
       </c>
@@ -2999,7 +2998,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>45</v>
       </c>
@@ -3010,7 +3009,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>45</v>
       </c>
@@ -3021,7 +3020,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>46</v>
       </c>
@@ -3032,7 +3031,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>46</v>
       </c>
@@ -3043,7 +3042,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>46</v>
       </c>
@@ -3054,7 +3053,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>46</v>
       </c>
@@ -3065,7 +3064,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>119</v>
       </c>
@@ -3076,7 +3075,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>119</v>
       </c>
@@ -3087,7 +3086,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>119</v>
       </c>
@@ -3098,7 +3097,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>43</v>
       </c>
@@ -3109,7 +3108,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>43</v>
       </c>
@@ -3120,7 +3119,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>43</v>
       </c>
@@ -3131,7 +3130,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>43</v>
       </c>
@@ -3142,7 +3141,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>43</v>
       </c>
@@ -3153,7 +3152,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>43</v>
       </c>
@@ -3164,7 +3163,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>43</v>
       </c>
@@ -3175,7 +3174,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>123</v>
       </c>
@@ -3186,7 +3185,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>123</v>
       </c>
@@ -3197,7 +3196,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>123</v>
       </c>
@@ -3208,7 +3207,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>125</v>
       </c>
@@ -3219,7 +3218,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>125</v>
       </c>
@@ -3230,7 +3229,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>125</v>
       </c>
@@ -3241,7 +3240,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>41</v>
       </c>
@@ -3252,7 +3251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>41</v>
       </c>
@@ -3263,7 +3262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>41</v>
       </c>
@@ -3274,7 +3273,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>41</v>
       </c>
@@ -3285,7 +3284,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>41</v>
       </c>
@@ -3296,7 +3295,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>41</v>
       </c>
@@ -3307,7 +3306,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>41</v>
       </c>
@@ -3318,7 +3317,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>41</v>
       </c>
@@ -3329,7 +3328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>41</v>
       </c>
@@ -3340,7 +3339,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>41</v>
       </c>
@@ -3351,7 +3350,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>41</v>
       </c>
@@ -3362,7 +3361,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>41</v>
       </c>
@@ -3373,7 +3372,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>41</v>
       </c>
@@ -3384,7 +3383,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>41</v>
       </c>
@@ -3395,7 +3394,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>41</v>
       </c>
@@ -3406,7 +3405,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>41</v>
       </c>
@@ -3417,7 +3416,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>41</v>
       </c>
@@ -3428,7 +3427,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>41</v>
       </c>
@@ -3439,7 +3438,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>41</v>
       </c>
@@ -3450,7 +3449,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>41</v>
       </c>
@@ -3462,14 +3461,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I178" xr:uid="{277571F3-9504-4C86-8E2D-BA4CDF05B089}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="COSTCO"/>
-        <filter val="TRADERS"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I178" xr:uid="{277571F3-9504-4C86-8E2D-BA4CDF05B089}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;"Calibri"&amp;10&amp;K000000 Business Use&amp;1#_x000D_</oddHeader>
@@ -3481,17 +3473,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6c0e7a184c0233f586ea7baba2e967b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6204f9fca8cd82ddbd42930875406446" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e6a91fd3482d498bd0f2490cb427e71">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2fe6c3346d7485db00f285dad19f0337" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -3712,6 +3695,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3724,28 +3716,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EACBF99-D736-43FE-9270-8EAAE9693B9F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{858AC7D4-6D6D-43B3-89B1-2B344252ACCC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CB27180-59BD-4819-98AD-8351D161500A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="57147975-5687-4135-8263-39f5df548c17"/>
-    <ds:schemaRef ds:uri="96d24a6b-8465-4498-bb54-acea15c87a74"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/HAIR_FFU_CHECKLIST.xlsx
+++ b/HAIR_FFU_CHECKLIST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pgone.sharepoint.com/sites/POpriority/Shared Documents/Project Eagles/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwon.w\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{E10D6F3C-833B-4FC8-B55E-879DB113DA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6851CAF-6EEA-44B9-A366-D5CC6D4B8775}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BA53A0E-7192-48A8-8FD0-EF9849191C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{7BDEC216-E803-42B4-BF8A-9FDE670B68F3}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$179</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="139">
   <si>
     <t xml:space="preserve">CUSTOMER </t>
   </si>
@@ -819,13 +819,6 @@
     </r>
   </si>
   <si>
-    <t>1200×1000mm (Min 1124×940mm)</t>
-  </si>
-  <si>
-    <t>1. Think wall issue in current tray to be fixed
-2. No fixed dimension on tray dimension</t>
-  </si>
-  <si>
     <t>FEFO - supply of products that have earlier manufacturing/expiry date than the latest supply is not accepted</t>
   </si>
   <si>
@@ -898,6 +891,28 @@
   </si>
   <si>
     <t>CS SPECIAL PACKAGING (FRAGILE ITEMS)</t>
+  </si>
+  <si>
+    <t>MAX 18kg</t>
+  </si>
+  <si>
+    <t>KPP- Black 1,016 * 1,219 * 150mm or AJ- Grey 1,020 * 1,218 * 150mm plastic pallets only</t>
+  </si>
+  <si>
+    <t>1219×1016mm ( ≈1200×1000mm w/ round corners)</t>
+  </si>
+  <si>
+    <t>1. Think wall issue in current tray to be fixed
+2. No fixed dimension on tray dimension except for under should width</t>
+  </si>
+  <si>
+    <t>1100×1100mm</t>
+  </si>
+  <si>
+    <t>1300mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ- Green 1,100 * 1,100 * 150mm plastic pallets only </t>
   </si>
 </sst>
 </file>
@@ -1490,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{277571F3-9504-4C86-8E2D-BA4CDF05B089}">
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -1712,7 +1727,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>66</v>
@@ -1723,7 +1738,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>67</v>
@@ -2130,7 +2145,7 @@
         <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>66</v>
@@ -2141,7 +2156,7 @@
         <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>67</v>
@@ -2460,7 +2475,7 @@
         <v>30</v>
       </c>
       <c r="B88" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>67</v>
@@ -2705,7 +2720,7 @@
         <v>4</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2771,7 +2786,7 @@
         <v>15</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2782,7 +2797,7 @@
         <v>71</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>72</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2823,36 +2838,37 @@
     </row>
     <row r="121" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B121" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="I121" s="8"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>38</v>
       </c>
       <c r="B122" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>111</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="I122" s="8"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>38</v>
       </c>
       <c r="B123" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -2863,29 +2879,29 @@
         <v>9</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>38</v>
       </c>
       <c r="B125" t="s">
-        <v>35</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>38</v>
       </c>
       <c r="B126" t="s">
-        <v>93</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>112</v>
+        <v>35</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -2893,21 +2909,21 @@
         <v>38</v>
       </c>
       <c r="B127" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>38</v>
       </c>
       <c r="B128" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -2915,10 +2931,10 @@
         <v>38</v>
       </c>
       <c r="B129" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -2926,10 +2942,10 @@
         <v>38</v>
       </c>
       <c r="B130" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -2937,10 +2953,10 @@
         <v>38</v>
       </c>
       <c r="B131" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -2948,54 +2964,54 @@
         <v>38</v>
       </c>
       <c r="B132" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>38</v>
       </c>
       <c r="B133" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>38</v>
       </c>
       <c r="B134" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>38</v>
       </c>
       <c r="B135" t="s">
+        <v>25</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>38</v>
+      </c>
+      <c r="B136" t="s">
         <v>87</v>
       </c>
-      <c r="C135" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>45</v>
-      </c>
-      <c r="B136" t="s">
-        <v>9</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>99</v>
+      <c r="C136" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3003,32 +3019,32 @@
         <v>45</v>
       </c>
       <c r="B137" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>45</v>
       </c>
       <c r="B138" t="s">
+        <v>22</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>45</v>
+      </c>
+      <c r="B139" t="s">
         <v>87</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>46</v>
-      </c>
-      <c r="B139" t="s">
-        <v>4</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>39</v>
+      <c r="C139" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3036,10 +3052,10 @@
         <v>46</v>
       </c>
       <c r="B140" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3047,10 +3063,10 @@
         <v>46</v>
       </c>
       <c r="B141" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3058,109 +3074,109 @@
         <v>46</v>
       </c>
       <c r="B142" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="B143" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B145" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>117</v>
+      </c>
+      <c r="B146" t="s">
         <v>22</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C146" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>43</v>
-      </c>
-      <c r="B146" t="s">
-        <v>47</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>43</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>43</v>
       </c>
       <c r="B148" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>43</v>
       </c>
       <c r="B149" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>43</v>
       </c>
       <c r="B150" t="s">
-        <v>13</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>43</v>
       </c>
       <c r="B151" t="s">
-        <v>22</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>97</v>
+        <v>13</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3168,87 +3184,87 @@
         <v>43</v>
       </c>
       <c r="B152" t="s">
+        <v>22</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>43</v>
+      </c>
+      <c r="B153" t="s">
         <v>87</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="C153" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>121</v>
+      </c>
+      <c r="B154" t="s">
+        <v>47</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>123</v>
-      </c>
-      <c r="B153" t="s">
-        <v>47</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>123</v>
-      </c>
-      <c r="B154" t="s">
-        <v>9</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>121</v>
+      </c>
+      <c r="B155" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>121</v>
+      </c>
+      <c r="B156" t="s">
+        <v>22</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>123</v>
       </c>
-      <c r="B155" t="s">
-        <v>22</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>125</v>
-      </c>
-      <c r="B156" t="s">
+      <c r="B157" t="s">
         <v>47</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>125</v>
-      </c>
-      <c r="B157" t="s">
-        <v>9</v>
-      </c>
       <c r="C157" s="1" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B158" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="B159" t="s">
-        <v>4</v>
-      </c>
-      <c r="C159" s="9" t="s">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3256,10 +3272,10 @@
         <v>41</v>
       </c>
       <c r="B160" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3270,7 +3286,7 @@
         <v>6</v>
       </c>
       <c r="C161" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -3278,10 +3294,10 @@
         <v>41</v>
       </c>
       <c r="B162" t="s">
-        <v>9</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>99</v>
+        <v>6</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -3292,10 +3308,10 @@
         <v>9</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>41</v>
       </c>
@@ -3303,18 +3319,18 @@
         <v>9</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>41</v>
       </c>
       <c r="B165" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -3322,10 +3338,10 @@
         <v>41</v>
       </c>
       <c r="B166" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -3336,7 +3352,7 @@
         <v>60</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -3344,10 +3360,10 @@
         <v>41</v>
       </c>
       <c r="B168" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -3355,21 +3371,21 @@
         <v>41</v>
       </c>
       <c r="B169" t="s">
-        <v>133</v>
+        <v>11</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>41</v>
       </c>
       <c r="B170" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -3377,21 +3393,21 @@
         <v>41</v>
       </c>
       <c r="B171" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>41</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -3399,10 +3415,10 @@
         <v>41</v>
       </c>
       <c r="B173" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -3410,10 +3426,10 @@
         <v>41</v>
       </c>
       <c r="B174" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -3421,13 +3437,13 @@
         <v>41</v>
       </c>
       <c r="B175" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>41</v>
       </c>
@@ -3435,33 +3451,44 @@
         <v>21</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>41</v>
       </c>
       <c r="B177" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>41</v>
       </c>
       <c r="B178" t="s">
+        <v>22</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>41</v>
+      </c>
+      <c r="B179" t="s">
         <v>87</v>
       </c>
-      <c r="C178" s="2" t="s">
-        <v>132</v>
+      <c r="C179" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I178" xr:uid="{277571F3-9504-4C86-8E2D-BA4CDF05B089}"/>
+  <autoFilter ref="A1:I179" xr:uid="{277571F3-9504-4C86-8E2D-BA4CDF05B089}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;"Calibri"&amp;10&amp;K000000 Business Use&amp;1#_x000D_</oddHeader>
@@ -3473,8 +3500,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e6a91fd3482d498bd0f2490cb427e71">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2fe6c3346d7485db00f285dad19f0337" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bed13c56006c51b90ac333a6ae976798">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eefb45b713b0d33d9a84026b36f62d67" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -3495,6 +3522,7 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3552,6 +3580,11 @@
     <xsd:element name="MediaServiceEventHashCode" ma:index="20" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3696,15 +3729,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="57147975-5687-4135-8263-39f5df548c17">
@@ -3715,19 +3739,20 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EACBF99-D736-43FE-9270-8EAAE9693B9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6C4456D-9489-48B9-9949-781332CB82AB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{858AC7D4-6D6D-43B3-89B1-2B344252ACCC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C76A210F-437A-4119-9DFA-CFDD2A427257}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3736,4 +3761,12 @@
     <ds:schemaRef ds:uri="96d24a6b-8465-4498-bb54-acea15c87a74"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{858AC7D4-6D6D-43B3-89B1-2B344252ACCC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/HAIR_FFU_CHECKLIST.xlsx
+++ b/HAIR_FFU_CHECKLIST.xlsx
@@ -3500,8 +3500,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bed13c56006c51b90ac333a6ae976798">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eefb45b713b0d33d9a84026b36f62d67" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d9416936a3b57ab26e55784844af5429">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9218ed845bf90baf0025c167a9057e7b" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -3523,6 +3523,7 @@
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:i0f84bba906045b4af568ee102a52dcb" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3626,6 +3627,13 @@
             </xsd:sequence>
           </xsd:extension>
         </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="i0f84bba906045b4af568ee102a52dcb" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="i0f84bba906045b4af568ee102a52dcb" ma:taxonomyFieldName="RevIMBCS" ma:displayName="Retention Policy" ma:indexed="true" ma:default="5;#Daily Work Documents [Standard]|c1df7c93-bf29-4bb4-a9f3-5b7aacc5e62b" ma:fieldId="{20f84bba-9060-45b4-af56-8ee102a52dcb}" ma:sspId="c81b625c-6132-4315-8b99-2d7d4df07560" ma:termSetId="1d8deb5c-7ccc-4e04-a1de-f52ad8333138" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
@@ -3734,7 +3742,17 @@
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="57147975-5687-4135-8263-39f5df548c17">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="96d24a6b-8465-4498-bb54-acea15c87a74" xsi:nil="true"/>
+    <TaxCatchAll xmlns="96d24a6b-8465-4498-bb54-acea15c87a74">
+      <Value>5</Value>
+    </TaxCatchAll>
+    <i0f84bba906045b4af568ee102a52dcb xmlns="96d24a6b-8465-4498-bb54-acea15c87a74">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Daily Work Documents [Standard]</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1df7c93-bf29-4bb4-a9f3-5b7aacc5e62b</TermId>
+        </TermInfo>
+      </Terms>
+    </i0f84bba906045b4af568ee102a52dcb>
   </documentManagement>
 </p:properties>
 </file>
@@ -3749,7 +3767,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6C4456D-9489-48B9-9949-781332CB82AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{608AA1D8-FBDB-409E-9354-1CD4A017A57E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
